--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\For Other\fehed\Tech\TechInnoSphere-Single\TechInnoSphere\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1174775-0AE1-41A8-B304-3E57EF887224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC50947-B23A-4202-9B3D-0FE544718D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="127">
   <si>
     <t>Title</t>
   </si>
@@ -386,16 +386,39 @@
   </si>
   <si>
     <t>https://drive.google.com/uc?export=view&amp;id=1TUqeKucxkr4dbj4K2F1lsGwlONvlWG--</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1ZWq-WUoD8GIkoX_VhZt8RpttCVBUPGlY</t>
+  </si>
+  <si>
+    <t>https://www.sweezenfoundation.org/</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1uvEKVKwClC7txLzQsjbMM1QvAPcaGNx</t>
+  </si>
+  <si>
+    <t>https://www.pmksteeliron.com/</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1J7JE3clFOBsot0MXZ2aibhUBIvDgvl0V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -418,10 +441,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -433,8 +457,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -772,8 +798,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
@@ -793,7 +819,7 @@
     <col min="18" max="18" width="20.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -905,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -961,7 +987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -980,8 +1006,8 @@
       <c r="F4" t="s">
         <v>83</v>
       </c>
-      <c r="G4" t="s">
-        <v>23</v>
+      <c r="G4" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="H4" t="s">
         <v>23</v>
@@ -1017,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -1040,7 +1066,7 @@
         <v>119</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="I5" t="s">
         <v>96</v>
@@ -1073,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -1129,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>69</v>
       </c>
@@ -1148,11 +1174,11 @@
       <c r="F7" t="s">
         <v>72</v>
       </c>
-      <c r="G7" t="s">
-        <v>120</v>
+      <c r="G7" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="I7" t="s">
         <v>73</v>
@@ -1185,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -1204,8 +1230,8 @@
       <c r="F8" t="s">
         <v>93</v>
       </c>
-      <c r="G8" t="s">
-        <v>23</v>
+      <c r="G8" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="H8" t="s">
         <v>23</v>
@@ -1297,16 +1323,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:18" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G7" r:id="rId1" xr:uid="{0D3FBEA7-ABEE-478D-B3BC-21F319DCAD3D}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{B13F0E4F-4448-43FD-89A9-AC5AADDE8BB8}"/>
+    <hyperlink ref="G8" r:id="rId3" xr:uid="{52FA3A80-330D-4815-9B69-F85C31BFDB96}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:R1 A7:F7 A4 E4 G4:H4 A8:E8 G8:N8 K4 A5:F5 J5:N5 Q4:R4 Q5:R5 A6:F6 Q6:R6 Q7:R7 Q8:R8 A3:F3 A2:F2 H2:R2 H3:R3 H5 H6:N6 H7:N7" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\For Other\fehed\Tech\TechInnoSphere-Single\TechInnoSphere\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC50947-B23A-4202-9B3D-0FE544718D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD276AAD-9421-45C0-B239-CDCF488A4E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -394,13 +394,13 @@
     <t>https://www.sweezenfoundation.org/</t>
   </si>
   <si>
-    <t>https://drive.google.com/uc?export=view&amp;id=1uvEKVKwClC7txLzQsjbMM1QvAPcaGNx</t>
-  </si>
-  <si>
     <t>https://www.pmksteeliron.com/</t>
   </si>
   <si>
     <t>https://drive.google.com/uc?export=view&amp;id=1J7JE3clFOBsot0MXZ2aibhUBIvDgvl0V</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=view&amp;id=1uvEKVKwClC7txLzQsjbMM1QvAPcaGNx_</t>
   </si>
 </sst>
 </file>
@@ -806,7 +806,7 @@
     <col min="3" max="3" width="43.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="255.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="86.59765625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="38.69921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.19921875" bestFit="1" customWidth="1"/>
@@ -1175,10 +1175,10 @@
         <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H7" t="s">
         <v>124</v>
-      </c>
-      <c r="H7" t="s">
-        <v>125</v>
       </c>
       <c r="I7" t="s">
         <v>73</v>
@@ -1231,7 +1231,7 @@
         <v>93</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
         <v>23</v>
